--- a/table3.xlsx
+++ b/table3.xlsx
@@ -37,7 +37,7 @@
     <t xml:space="preserve">    stage 2</t>
   </si>
   <si>
-    <t xml:space="preserve">n/N (%)</t>
+    <t xml:space="preserve">n (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
@@ -55,16 +55,16 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">31,028.00/155,138.00 (20.00%) (19.80%, 20.20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,484.00/155,138.00 (11.91%) (11.75%, 12.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55,305.00/155,138.00 (35.65%) (35.41%, 35.89%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50,321.00/155,138.00 (32.44%) (32.20%, 32.67%)</t>
+    <t xml:space="preserve">31,028 (20.00%) (19.80%, 20.20%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,484 (11.91%) (11.75%, 12.08%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55,305 (35.65%) (35.41%, 35.89%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,321 (32.44%) (32.20%, 32.67%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -72,16 +72,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">12,888.00/120,381.00 (10.71%) (10.53%, 10.88%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,951.00/120,381.00 (9.93%) (9.760%, 10.10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,754.00/120,381.00 (33.85%) (33.59%, 34.12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54,788.00/120,381.00 (45.51%) (45.23%, 45.79%)</t>
+    <t xml:space="preserve">12,888 (10.71%) (10.53%, 10.88%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,951 (9.93%) (9.760%, 10.10%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,754 (33.85%) (33.59%, 34.12%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,788 (45.51%) (45.23%, 45.79%)</t>
   </si>
   <si>
     <t xml:space="preserve">White
@@ -93,16 +93,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">647,441.00/2,799,460.00 (23.13%) (23.08%, 23.18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327,568.00/2,799,460.00 (11.70%) (11.66%, 11.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,004,044.00/2,799,460.00 (35.87%) (35.81%, 35.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">820,407.00/2,799,460.00 (29.31%) (29.25%, 29.36%)</t>
+    <t xml:space="preserve">647,441 (23.13%) (23.08%, 23.18%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327,568 (11.70%) (11.66%, 11.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,004,044 (35.87%) (35.81%, 35.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">820,407 (29.31%) (29.25%, 29.36%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -110,16 +110,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">216,950.00/2,337,936.00 (9.28%) (9.242%, 9.317%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208,063.00/2,337,936.00 (8.90%) (8.863%, 8.936%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">769,655.00/2,337,936.00 (32.92%) (32.86%, 32.98%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,143,268.00/2,337,936.00 (48.90%) (48.84%, 48.96%)</t>
+    <t xml:space="preserve">216,950 (9.28%) (9.242%, 9.317%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208,063 (8.90%) (8.863%, 8.936%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">769,655 (32.92%) (32.86%, 32.98%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,143,268 (48.90%) (48.84%, 48.96%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other
@@ -131,16 +131,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">140,217.00/402,795.00 (34.81%) (34.66%, 34.96%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47,412.00/402,795.00 (11.77%) (11.67%, 11.87%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134,904.00/402,795.00 (33.49%) (33.35%, 33.64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80,262.00/402,795.00 (19.93%) (19.80%, 20.05%)</t>
+    <t xml:space="preserve">140,217 (34.81%) (34.66%, 34.96%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47,412 (11.77%) (11.67%, 11.87%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134,904 (33.49%) (33.35%, 33.64%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80,262 (19.93%) (19.80%, 20.05%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -148,16 +148,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">58,343.00/376,944.00 (15.48%) (15.36%, 15.59%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,495.00/376,944.00 (10.74%) (10.64%, 10.84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135,935.00/376,944.00 (36.06%) (35.91%, 36.22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,171.00/376,944.00 (37.72%) (37.56%, 37.87%)</t>
+    <t xml:space="preserve">58,343 (15.48%) (15.36%, 15.59%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,495 (10.74%) (10.64%, 10.84%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135,935 (36.06%) (35.91%, 36.22%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,171 (37.72%) (37.56%, 37.87%)</t>
   </si>
 </sst>
 </file>

--- a/table3.xlsx
+++ b/table3.xlsx
@@ -174,13 +174,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <b/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>

--- a/table3.xlsx
+++ b/table3.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t xml:space="preserve">
 </t>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t xml:space="preserve">n (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbreviation: CI = Confidence Interval</t>
   </si>
   <si>
     <t xml:space="preserve">Black
@@ -55,16 +52,16 @@
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">31,028 (20.00%) (19.80%, 20.20%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,484 (11.91%) (11.75%, 12.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55,305 (35.65%) (35.41%, 35.89%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50,321 (32.44%) (32.20%, 32.67%)</t>
+    <t xml:space="preserve">31,028 (20.00%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18,484 (11.91%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55,305 (35.65%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50,321 (32.44%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -72,16 +69,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">12,888 (10.71%) (10.53%, 10.88%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11,951 (9.93%) (9.760%, 10.10%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,754 (33.85%) (33.59%, 34.12%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54,788 (45.51%) (45.23%, 45.79%)</t>
+    <t xml:space="preserve">12,888 (10.71%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11,951 (9.93%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,754 (33.85%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54,788 (45.51%)</t>
   </si>
   <si>
     <t xml:space="preserve">White
@@ -93,16 +90,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">647,441 (23.13%) (23.08%, 23.18%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">327,568 (11.70%) (11.66%, 11.74%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,004,044 (35.87%) (35.81%, 35.92%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">820,407 (29.31%) (29.25%, 29.36%)</t>
+    <t xml:space="preserve">647,441 (23.13%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">327,568 (11.70%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,004,044 (35.87%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">820,407 (29.31%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -110,16 +107,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">216,950 (9.28%) (9.242%, 9.317%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208,063 (8.90%) (8.863%, 8.936%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">769,655 (32.92%) (32.86%, 32.98%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,143,268 (48.90%) (48.84%, 48.96%)</t>
+    <t xml:space="preserve">216,950 (9.28%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">208,063 (8.90%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">769,655 (32.92%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,143,268 (48.90%)</t>
   </si>
   <si>
     <t xml:space="preserve">Other
@@ -131,16 +128,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">140,217 (34.81%) (34.66%, 34.96%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47,412 (11.77%) (11.67%, 11.87%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134,904 (33.49%) (33.35%, 33.64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80,262 (19.93%) (19.80%, 20.05%)</t>
+    <t xml:space="preserve">140,217 (34.81%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47,412 (11.77%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">134,904 (33.49%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">80,262 (19.93%)</t>
   </si>
   <si>
     <t xml:space="preserve">M
@@ -148,16 +145,16 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">58,343 (15.48%) (15.36%, 15.59%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40,495 (10.74%) (10.64%, 10.84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">135,935 (36.06%) (35.91%, 36.22%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">142,171 (37.72%) (37.56%, 37.87%)</t>
+    <t xml:space="preserve">58,343 (15.48%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40,495 (10.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">135,935 (36.06%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">142,171 (37.72%)</t>
   </si>
 </sst>
 </file>
@@ -193,7 +190,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -267,20 +264,6 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="none">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="none">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="none">
         <color rgb="FF000000"/>
       </bottom>
@@ -289,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
@@ -307,9 +290,6 @@
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment textRotation="0" horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -630,161 +610,161 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>32</v>
+      <c r="B1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" ht="NA" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>38</v>
+      <c r="B2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="NA" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="10" t="s">
-        <v>11</v>
+      <c r="B3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" ht="NA" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>39</v>
+      <c r="B4" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" ht="NA" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>40</v>
+      <c r="B5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" ht="NA" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>41</v>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7" ht="NA" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>42</v>
+      <c r="B7" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="NA" customHeight="1">
@@ -810,33 +790,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" ht="NA" customHeight="1">
-      <c r="A9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A8:G8"/>
-    <mergeCell ref="A9:G9"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
